--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2732-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2732-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9A3DB14-F5B2-434B-9C89-C540BCE1E8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28FBAFC8-1CE2-4638-9FCE-BC31BD317061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{CABF8C5A-EB69-41CB-B6E5-95C66970C2B1}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{85100405-A9E8-44D3-AFC6-80A9B1631E1C}"/>
   </bookViews>
   <sheets>
     <sheet name="2732-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1499,27 +1499,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD2C671-781E-4BA0-81FC-1F671131672E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AF9C516-628E-4545-BF38-E1D592DC9879}">
   <dimension ref="A1:X43"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="24" width="8.125" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="7" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1553,7 +1554,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1589,7 +1590,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1641,7 +1642,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1709,7 +1710,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1781,7 +1782,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1855,7 +1856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1929,7 +1930,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2003,7 +2004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2024</v>
       </c>
@@ -2075,7 +2076,7 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2149,7 +2150,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2223,7 +2224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2297,7 +2298,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2371,7 +2372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2023</v>
       </c>
@@ -2443,7 +2444,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2517,7 +2518,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2591,7 +2592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2665,7 +2666,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2739,7 +2740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2022</v>
       </c>
@@ -2811,7 +2812,7 @@
         <v>6.53</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2885,7 +2886,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -2959,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3033,7 +3034,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3107,7 +3108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2021</v>
       </c>
@@ -3179,7 +3180,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>29</v>
       </c>
@@ -3253,7 +3254,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3327,7 +3328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -3401,7 +3402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>29</v>
       </c>
@@ -3475,7 +3476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3549,7 +3550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3623,7 +3624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2020</v>
       </c>
@@ -3695,7 +3696,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>29</v>
       </c>
@@ -3769,7 +3770,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>29</v>
       </c>
@@ -3843,7 +3844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>29</v>
       </c>
@@ -3917,7 +3918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2019</v>
       </c>
@@ -3989,7 +3990,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2018</v>
       </c>
@@ -4061,7 +4062,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2017</v>
       </c>
@@ -4133,7 +4134,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2016</v>
       </c>
@@ -4205,7 +4206,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>2015</v>
       </c>
@@ -4277,7 +4278,7 @@
         <v>7.91</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>2014</v>
       </c>
@@ -4349,7 +4350,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>2013</v>
       </c>
@@ -4421,7 +4422,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2012</v>
       </c>
@@ -4493,7 +4494,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="35" t="s">
         <v>54</v>
       </c>
